--- a/data/file_generation/reference/data_383/身份证号重复人员统计_res.xlsx
+++ b/data/file_generation/reference/data_383/身份证号重复人员统计_res.xlsx
@@ -1,42 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxin1/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxin1/Desktop/datasets/数据分析/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FB036C-F64D-B648-9566-F4C4F924FBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF998E3-75C4-C94C-8070-64347324A28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="171">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>身份证号</t>
   </si>
@@ -53,106 +40,499 @@
     <t>年龄</t>
   </si>
   <si>
-    <t>******193505027503</t>
-  </si>
-  <si>
-    <t>user_20</t>
-  </si>
-  <si>
-    <t>dx60 周岁以上人员名单_按地址排序 - 已排除已入住_匿名化.xlsx</t>
-  </si>
-  <si>
-    <t>项山路</t>
-  </si>
-  <si>
-    <t>不愿意来院入住的_匿名化.xlsx</t>
-  </si>
-  <si>
-    <t>******193901040021</t>
-  </si>
-  <si>
-    <t>user_21</t>
-  </si>
-  <si>
-    <t>上城壕</t>
-  </si>
-  <si>
-    <t>******194501210807</t>
-  </si>
-  <si>
-    <t>user_30</t>
-  </si>
-  <si>
-    <t>解放南路</t>
-  </si>
-  <si>
-    <t>******194901090031</t>
-  </si>
-  <si>
-    <t>user_19</t>
-  </si>
-  <si>
-    <t>西街</t>
-  </si>
-  <si>
-    <t>******195011076339</t>
-  </si>
-  <si>
-    <t>user_38</t>
-  </si>
-  <si>
-    <t>解放中路</t>
-  </si>
-  <si>
-    <t>******195205050014</t>
-  </si>
-  <si>
-    <t>user_15</t>
-  </si>
-  <si>
-    <t>新市街</t>
-  </si>
-  <si>
-    <t>******195910297370</t>
-  </si>
-  <si>
-    <t>user_18</t>
-  </si>
-  <si>
-    <t>******196205066053</t>
-  </si>
-  <si>
-    <t>user_16</t>
-  </si>
-  <si>
-    <t>东街</t>
-  </si>
-  <si>
-    <t>******196306020492</t>
-  </si>
-  <si>
-    <t>user_29</t>
-  </si>
-  <si>
-    <t>******19630714725X</t>
-  </si>
-  <si>
-    <t>user_26</t>
-  </si>
-  <si>
-    <t>学坝街</t>
-  </si>
-  <si>
-    <t>******196310100495</t>
-  </si>
-  <si>
-    <t>user_25</t>
-  </si>
-  <si>
-    <t>******196507165740</t>
-  </si>
-  <si>
-    <t>user_10</t>
+    <t>ID-001</t>
+  </si>
+  <si>
+    <t>usr-126</t>
+  </si>
+  <si>
+    <t>dx60 周岁以上人员名单_按地址排序 - 已排除已入住.xlsx</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>usr-036</t>
+  </si>
+  <si>
+    <t>pj60 周岁以上不含村字人员名单.xlsx</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>不愿意来院入住的.xlsx</t>
+  </si>
+  <si>
+    <t>site-038</t>
+  </si>
+  <si>
+    <t>ID-002</t>
+  </si>
+  <si>
+    <t>usr-026</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>usr-012</t>
+  </si>
+  <si>
+    <t>site-032</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>ID-003</t>
+  </si>
+  <si>
+    <t>usr-111</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>usr-028</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>ID-005</t>
+  </si>
+  <si>
+    <t>usr-006</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>usr-038</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>site-023</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>ID-006</t>
+  </si>
+  <si>
+    <t>usr-015</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>usr-100</t>
+  </si>
+  <si>
+    <t>site-006</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>ID-007</t>
+  </si>
+  <si>
+    <t>usr-053</t>
+  </si>
+  <si>
+    <t>usr-049</t>
+  </si>
+  <si>
+    <t>site-029</t>
+  </si>
+  <si>
+    <t>ID-008</t>
+  </si>
+  <si>
+    <t>usr-090</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>usr-011</t>
+  </si>
+  <si>
+    <t>ID-009</t>
+  </si>
+  <si>
+    <t>usr-063</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>usr-020</t>
+  </si>
+  <si>
+    <t>site-018</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>ID-010</t>
+  </si>
+  <si>
+    <t>usr-041</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>usr-083</t>
+  </si>
+  <si>
+    <t>site-035</t>
+  </si>
+  <si>
+    <t>ID-011</t>
+  </si>
+  <si>
+    <t>usr-009</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>usr-066</t>
+  </si>
+  <si>
+    <t>site-030</t>
+  </si>
+  <si>
+    <t>ID-012</t>
+  </si>
+  <si>
+    <t>usr-065</t>
+  </si>
+  <si>
+    <t>usr-042</t>
+  </si>
+  <si>
+    <t>site-013</t>
+  </si>
+  <si>
+    <t>ID-013</t>
+  </si>
+  <si>
+    <t>usr-077</t>
+  </si>
+  <si>
+    <t>usr-055</t>
+  </si>
+  <si>
+    <t>ID-014</t>
+  </si>
+  <si>
+    <t>usr-089</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>usr-044</t>
+  </si>
+  <si>
+    <t>site-008</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>ID-015</t>
+  </si>
+  <si>
+    <t>usr-016</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>usr-062</t>
+  </si>
+  <si>
+    <t>site-004</t>
+  </si>
+  <si>
+    <t>ID-017</t>
+  </si>
+  <si>
+    <t>usr-081</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>usr-102</t>
+  </si>
+  <si>
+    <t>site-022</t>
+  </si>
+  <si>
+    <t>ID-018</t>
+  </si>
+  <si>
+    <t>usr-106</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>usr-019</t>
+  </si>
+  <si>
+    <t>site-031</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>ID-019</t>
+  </si>
+  <si>
+    <t>usr-046</t>
+  </si>
+  <si>
+    <t>usr-093</t>
+  </si>
+  <si>
+    <t>ID-020</t>
+  </si>
+  <si>
+    <t>usr-064</t>
+  </si>
+  <si>
+    <t>usr-101</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>ID-021</t>
+  </si>
+  <si>
+    <t>usr-113</t>
+  </si>
+  <si>
+    <t>usr-050</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ID-022</t>
+  </si>
+  <si>
+    <t>usr-010</t>
+  </si>
+  <si>
+    <t>usr-085</t>
+  </si>
+  <si>
+    <t>site-003</t>
+  </si>
+  <si>
+    <t>ID-023</t>
+  </si>
+  <si>
+    <t>usr-047</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>usr-092</t>
+  </si>
+  <si>
+    <t>ID-024</t>
+  </si>
+  <si>
+    <t>usr-003</t>
+  </si>
+  <si>
+    <t>usr-122</t>
+  </si>
+  <si>
+    <t>site-021</t>
+  </si>
+  <si>
+    <t>ID-025</t>
+  </si>
+  <si>
+    <t>usr-069</t>
+  </si>
+  <si>
+    <t>usr-112</t>
+  </si>
+  <si>
+    <t>ID-026</t>
+  </si>
+  <si>
+    <t>usr-115</t>
+  </si>
+  <si>
+    <t>usr-017</t>
+  </si>
+  <si>
+    <t>ID-029</t>
+  </si>
+  <si>
+    <t>usr-052</t>
+  </si>
+  <si>
+    <t>usr-071</t>
+  </si>
+  <si>
+    <t>site-001</t>
+  </si>
+  <si>
+    <t>ID-030</t>
+  </si>
+  <si>
+    <t>usr-033</t>
+  </si>
+  <si>
+    <t>usr-008</t>
+  </si>
+  <si>
+    <t>site-019</t>
+  </si>
+  <si>
+    <t>ID-031</t>
+  </si>
+  <si>
+    <t>usr-073</t>
+  </si>
+  <si>
+    <t>usr-032</t>
+  </si>
+  <si>
+    <t>site-033</t>
+  </si>
+  <si>
+    <t>ID-032</t>
+  </si>
+  <si>
+    <t>usr-094</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>usr-001</t>
+  </si>
+  <si>
+    <t>site-007</t>
+  </si>
+  <si>
+    <t>ID-034</t>
+  </si>
+  <si>
+    <t>usr-023</t>
+  </si>
+  <si>
+    <t>usr-045</t>
+  </si>
+  <si>
+    <t>ID-035</t>
+  </si>
+  <si>
+    <t>usr-109</t>
+  </si>
+  <si>
+    <t>usr-103</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>ID-036</t>
+  </si>
+  <si>
+    <t>usr-068</t>
+  </si>
+  <si>
+    <t>usr-082</t>
+  </si>
+  <si>
+    <t>ID-038</t>
+  </si>
+  <si>
+    <t>usr-056</t>
+  </si>
+  <si>
+    <t>usr-057</t>
+  </si>
+  <si>
+    <t>site-036</t>
+  </si>
+  <si>
+    <t>ID-044</t>
+  </si>
+  <si>
+    <t>usr-118</t>
+  </si>
+  <si>
+    <t>site-002</t>
+  </si>
+  <si>
+    <t>ID-083</t>
+  </si>
+  <si>
+    <t>usr-051</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>site-012</t>
+  </si>
+  <si>
+    <t>ID-091</t>
+  </si>
+  <si>
+    <t>usr-040</t>
+  </si>
+  <si>
+    <t>usr-039</t>
+  </si>
+  <si>
+    <t>ID-105</t>
+  </si>
+  <si>
+    <t>usr-075</t>
+  </si>
+  <si>
+    <t>site-026</t>
+  </si>
+  <si>
+    <t>ID-107</t>
+  </si>
+  <si>
+    <t>usr-048</t>
+  </si>
+  <si>
+    <t>site-025</t>
+  </si>
+  <si>
+    <t>ID-108</t>
+  </si>
+  <si>
+    <t>usr-123</t>
+  </si>
+  <si>
+    <t>site-010</t>
   </si>
 </sst>
 </file>
@@ -524,13 +904,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="26.375" customWidth="1"/>
+    <col min="4" max="4" width="34.1640625" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,10 +927,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -560,363 +944,1460 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>5</v>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
         <v>10</v>
       </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C35" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" t="s">
+        <v>119</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" t="s">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>132</v>
+      </c>
+      <c r="F60" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" t="s">
+        <v>134</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>137</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" t="s">
+        <v>139</v>
+      </c>
+      <c r="D63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" t="s">
+        <v>149</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>151</v>
+      </c>
+      <c r="F71" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>154</v>
+      </c>
+      <c r="F73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
+        <v>156</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>155</v>
+      </c>
+      <c r="C75" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>158</v>
+      </c>
+      <c r="F75" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" t="s">
+        <v>163</v>
+      </c>
+      <c r="D78" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" t="s">
+        <v>163</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>164</v>
+      </c>
+      <c r="F79" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>165</v>
+      </c>
+      <c r="C80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25">
-        <v>60</v>
+      <c r="B81" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>167</v>
+      </c>
+      <c r="F81" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" t="s">
+        <v>169</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>170</v>
+      </c>
+      <c r="F83" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -926,15 +2407,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -1082,6 +2554,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1089,13 +2570,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24810A17-863B-490C-A0C3-871C685613DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81BD0416-B92A-43F4-837F-859F0F5A5590}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D51C24D6-9187-415E-822B-C8C32D88DD77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BCCF3BB-25A6-4DC5-AB67-3984A7C049DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B30A30-F63F-4742-BCD1-A3723EC1C0A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{133CAFEF-0EDE-4ABA-BE74-38AB1C4F3FD1}"/>
 </file>